--- a/output/reports/サンプル/データ1サンプル.xlsx
+++ b/output/reports/サンプル/データ1サンプル.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="96" yWindow="312" windowWidth="11868" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-168" yWindow="432" windowWidth="11868" windowHeight="12816" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" state="visible" r:id="rId1"/>
@@ -377,10 +377,10 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -967,7 +967,7 @@
   <dimension ref="C12:AB44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="11" ht="15" customHeight="1" thickBot="1"/>
@@ -1050,7 +1050,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>2026/07/02</t>
+          <t>2026/07/03</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
   <dimension ref="B2:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1087,7 +1087,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="B4" s="33" t="inlineStr">
         <is>
-          <t>AI（LightGBM回帰モデル）による未来予測では、対象児童2名の平均予測欠席日数は月あたり約1.0日と推定された。予測期間内に安定化が見込まれる児童はいなかった。継続的な健康観察と家庭との連携を強化し、個々の状況に応じた支援を継続することが望まれる。</t>
+          <t>AIによる予測では、対象児童2名の平均欠席日数は約1.0日と推定された。予測期間内に安定化が見込まれる児童はおらず、継続的な健康観察と家庭との連携が重要と考えられる。</t>
         </is>
       </c>
       <c r="C4" s="34" t="n"/>
@@ -1183,7 +1183,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>AI（LightGBM回帰モデル）による予測では、予測期間内に安定化が見込まれる児童は確認されなかった。今後も継続的な健康観察や家庭との連携を行いながら、児童一人ひとりの状況に応じた支援を継続することが重要である。本システムは欠席傾向を可視化し、継続的な健康管理を支援するための参考資料として活用できる。</t>
+          <t>AI予測では予測期間内に安定化が見込まれる児童は確認されなかった。継続的な健康観察と家庭との情報共有を行いながら、個々の状況に応じた支援を継続することが望まれる。</t>
         </is>
       </c>
       <c r="C16" s="34" t="n"/>
@@ -1289,7 +1289,7 @@
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1306,7 +1306,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1586,7 +1586,7 @@
   <dimension ref="B2:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -1598,7 +1598,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>■ 主な傾向</t>
         </is>
@@ -1637,12 +1637,10 @@
     <row r="6" ht="15" customHeight="1">
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>月齢別のデータが不足しているため、傾向は判定できませんでした。
-学年別のデータが不足しているため、傾向は判定できませんでした。
-登園月数別のデータが不足しているため、傾向は判定できませんでした。
-登園年数別のデータが不足しているため、傾向は判定できませんでした。
-月別の季節性のデータが不足しているため、傾向は判定できませんでした。
-月間推移のデータが不足しているため、傾向は判定できませんでした。</t>
+          <t>【子供001】
+データが不足しているため、判定できませんでした。
+【子供002】
+データが不足しているため、判定できませんでした。</t>
         </is>
       </c>
       <c r="C6" s="34" t="n"/>
@@ -1730,119 +1728,120 @@
       <c r="AC20" s="37" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
-      <c r="B21" s="38" t="n"/>
-      <c r="C21" s="32" t="n"/>
-      <c r="D21" s="32" t="n"/>
-      <c r="E21" s="32" t="n"/>
-      <c r="F21" s="32" t="n"/>
-      <c r="G21" s="32" t="n"/>
-      <c r="H21" s="32" t="n"/>
-      <c r="I21" s="32" t="n"/>
-      <c r="J21" s="32" t="n"/>
-      <c r="K21" s="32" t="n"/>
-      <c r="L21" s="32" t="n"/>
-      <c r="M21" s="32" t="n"/>
-      <c r="N21" s="32" t="n"/>
-      <c r="O21" s="32" t="n"/>
-      <c r="P21" s="32" t="n"/>
-      <c r="Q21" s="32" t="n"/>
-      <c r="R21" s="32" t="n"/>
-      <c r="S21" s="32" t="n"/>
-      <c r="T21" s="32" t="n"/>
-      <c r="U21" s="32" t="n"/>
-      <c r="V21" s="32" t="n"/>
-      <c r="W21" s="32" t="n"/>
-      <c r="X21" s="32" t="n"/>
-      <c r="Y21" s="32" t="n"/>
-      <c r="Z21" s="32" t="n"/>
-      <c r="AA21" s="32" t="n"/>
-      <c r="AB21" s="32" t="n"/>
-      <c r="AC21" s="39" t="n"/>
+      <c r="B21" s="36" t="n"/>
+      <c r="AC21" s="37" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="B22" s="30" t="inlineStr">
+      <c r="B22" s="36" t="n"/>
+      <c r="AC22" s="37" t="n"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="B23" s="36" t="n"/>
+      <c r="AC23" s="37" t="n"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="38" t="n"/>
+      <c r="C24" s="32" t="n"/>
+      <c r="D24" s="32" t="n"/>
+      <c r="E24" s="32" t="n"/>
+      <c r="F24" s="32" t="n"/>
+      <c r="G24" s="32" t="n"/>
+      <c r="H24" s="32" t="n"/>
+      <c r="I24" s="32" t="n"/>
+      <c r="J24" s="32" t="n"/>
+      <c r="K24" s="32" t="n"/>
+      <c r="L24" s="32" t="n"/>
+      <c r="M24" s="32" t="n"/>
+      <c r="N24" s="32" t="n"/>
+      <c r="O24" s="32" t="n"/>
+      <c r="P24" s="32" t="n"/>
+      <c r="Q24" s="32" t="n"/>
+      <c r="R24" s="32" t="n"/>
+      <c r="S24" s="32" t="n"/>
+      <c r="T24" s="32" t="n"/>
+      <c r="U24" s="32" t="n"/>
+      <c r="V24" s="32" t="n"/>
+      <c r="W24" s="32" t="n"/>
+      <c r="X24" s="32" t="n"/>
+      <c r="Y24" s="32" t="n"/>
+      <c r="Z24" s="32" t="n"/>
+      <c r="AA24" s="32" t="n"/>
+      <c r="AB24" s="32" t="n"/>
+      <c r="AC24" s="39" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="B25" s="31" t="inlineStr">
         <is>
           <t>■ 未来予測結果</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="B23" s="32" t="n"/>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="32" t="n"/>
-      <c r="E23" s="32" t="n"/>
-      <c r="F23" s="32" t="n"/>
-      <c r="G23" s="32" t="n"/>
-      <c r="H23" s="32" t="n"/>
-      <c r="I23" s="32" t="n"/>
-      <c r="J23" s="32" t="n"/>
-      <c r="K23" s="32" t="n"/>
-      <c r="L23" s="32" t="n"/>
-      <c r="M23" s="32" t="n"/>
-      <c r="N23" s="32" t="n"/>
-      <c r="O23" s="32" t="n"/>
-      <c r="P23" s="32" t="n"/>
-      <c r="Q23" s="32" t="n"/>
-      <c r="R23" s="32" t="n"/>
-      <c r="S23" s="32" t="n"/>
-      <c r="T23" s="32" t="n"/>
-      <c r="U23" s="32" t="n"/>
-      <c r="V23" s="32" t="n"/>
-      <c r="W23" s="32" t="n"/>
-      <c r="X23" s="32" t="n"/>
-      <c r="Y23" s="32" t="n"/>
-      <c r="Z23" s="32" t="n"/>
-      <c r="AA23" s="32" t="n"/>
-      <c r="AB23" s="32" t="n"/>
-      <c r="AC23" s="32" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="33" t="inlineStr">
-        <is>
-          <t>AI（LightGBM回帰モデル）による24か月先までの未来予測を実施した結果、以下の見通しが得られました。
-・子供001：予測期間中の平均欠席日数は約1.0日（1.0～1.0日）と推定された。予測期間内では安定基準に達しない可能性が示された。
-・子供002：予測期間中の平均欠席日数は約1.0日（1.0～1.0日）と推定された。予測期間内では安定基準に達しない可能性が示された。</t>
-        </is>
-      </c>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="34" t="n"/>
-      <c r="J24" s="34" t="n"/>
-      <c r="K24" s="34" t="n"/>
-      <c r="L24" s="34" t="n"/>
-      <c r="M24" s="34" t="n"/>
-      <c r="N24" s="34" t="n"/>
-      <c r="O24" s="34" t="n"/>
-      <c r="P24" s="34" t="n"/>
-      <c r="Q24" s="34" t="n"/>
-      <c r="R24" s="34" t="n"/>
-      <c r="S24" s="34" t="n"/>
-      <c r="T24" s="34" t="n"/>
-      <c r="U24" s="34" t="n"/>
-      <c r="V24" s="34" t="n"/>
-      <c r="W24" s="34" t="n"/>
-      <c r="X24" s="34" t="n"/>
-      <c r="Y24" s="34" t="n"/>
-      <c r="Z24" s="34" t="n"/>
-      <c r="AA24" s="34" t="n"/>
-      <c r="AB24" s="34" t="n"/>
-      <c r="AC24" s="35" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="B25" s="36" t="n"/>
-      <c r="AC25" s="37" t="n"/>
-    </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="36" t="n"/>
-      <c r="AC26" s="37" t="n"/>
+      <c r="B26" s="32" t="n"/>
+      <c r="C26" s="32" t="n"/>
+      <c r="D26" s="32" t="n"/>
+      <c r="E26" s="32" t="n"/>
+      <c r="F26" s="32" t="n"/>
+      <c r="G26" s="32" t="n"/>
+      <c r="H26" s="32" t="n"/>
+      <c r="I26" s="32" t="n"/>
+      <c r="J26" s="32" t="n"/>
+      <c r="K26" s="32" t="n"/>
+      <c r="L26" s="32" t="n"/>
+      <c r="M26" s="32" t="n"/>
+      <c r="N26" s="32" t="n"/>
+      <c r="O26" s="32" t="n"/>
+      <c r="P26" s="32" t="n"/>
+      <c r="Q26" s="32" t="n"/>
+      <c r="R26" s="32" t="n"/>
+      <c r="S26" s="32" t="n"/>
+      <c r="T26" s="32" t="n"/>
+      <c r="U26" s="32" t="n"/>
+      <c r="V26" s="32" t="n"/>
+      <c r="W26" s="32" t="n"/>
+      <c r="X26" s="32" t="n"/>
+      <c r="Y26" s="32" t="n"/>
+      <c r="Z26" s="32" t="n"/>
+      <c r="AA26" s="32" t="n"/>
+      <c r="AB26" s="32" t="n"/>
+      <c r="AC26" s="32" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
-      <c r="B27" s="36" t="n"/>
-      <c r="AC27" s="37" t="n"/>
+      <c r="B27" s="33" t="inlineStr">
+        <is>
+          <t>【子供001】
+データが不足しているため、判定できませんでした。
+【子供002】
+データが不足しているため、判定できませんでした。</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="34" t="n"/>
+      <c r="J27" s="34" t="n"/>
+      <c r="K27" s="34" t="n"/>
+      <c r="L27" s="34" t="n"/>
+      <c r="M27" s="34" t="n"/>
+      <c r="N27" s="34" t="n"/>
+      <c r="O27" s="34" t="n"/>
+      <c r="P27" s="34" t="n"/>
+      <c r="Q27" s="34" t="n"/>
+      <c r="R27" s="34" t="n"/>
+      <c r="S27" s="34" t="n"/>
+      <c r="T27" s="34" t="n"/>
+      <c r="U27" s="34" t="n"/>
+      <c r="V27" s="34" t="n"/>
+      <c r="W27" s="34" t="n"/>
+      <c r="X27" s="34" t="n"/>
+      <c r="Y27" s="34" t="n"/>
+      <c r="Z27" s="34" t="n"/>
+      <c r="AA27" s="34" t="n"/>
+      <c r="AB27" s="34" t="n"/>
+      <c r="AC27" s="35" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="36" t="n"/>
@@ -1857,124 +1856,124 @@
       <c r="AC30" s="37" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
-      <c r="B31" s="38" t="n"/>
-      <c r="C31" s="32" t="n"/>
-      <c r="D31" s="32" t="n"/>
-      <c r="E31" s="32" t="n"/>
-      <c r="F31" s="32" t="n"/>
-      <c r="G31" s="32" t="n"/>
-      <c r="H31" s="32" t="n"/>
-      <c r="I31" s="32" t="n"/>
-      <c r="J31" s="32" t="n"/>
-      <c r="K31" s="32" t="n"/>
-      <c r="L31" s="32" t="n"/>
-      <c r="M31" s="32" t="n"/>
-      <c r="N31" s="32" t="n"/>
-      <c r="O31" s="32" t="n"/>
-      <c r="P31" s="32" t="n"/>
-      <c r="Q31" s="32" t="n"/>
-      <c r="R31" s="32" t="n"/>
-      <c r="S31" s="32" t="n"/>
-      <c r="T31" s="32" t="n"/>
-      <c r="U31" s="32" t="n"/>
-      <c r="V31" s="32" t="n"/>
-      <c r="W31" s="32" t="n"/>
-      <c r="X31" s="32" t="n"/>
-      <c r="Y31" s="32" t="n"/>
-      <c r="Z31" s="32" t="n"/>
-      <c r="AA31" s="32" t="n"/>
-      <c r="AB31" s="32" t="n"/>
-      <c r="AC31" s="39" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="AC31" s="37" t="n"/>
+    </row>
+    <row r="32" ht="15" customHeight="1">
+      <c r="B32" s="36" t="n"/>
+      <c r="AC32" s="37" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
-      <c r="B33" s="30" t="inlineStr">
+      <c r="B33" s="36" t="n"/>
+      <c r="AC33" s="37" t="n"/>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="B34" s="36" t="n"/>
+      <c r="AC34" s="37" t="n"/>
+    </row>
+    <row r="35" ht="15" customHeight="1">
+      <c r="B35" s="38" t="n"/>
+      <c r="C35" s="32" t="n"/>
+      <c r="D35" s="32" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="32" t="n"/>
+      <c r="H35" s="32" t="n"/>
+      <c r="I35" s="32" t="n"/>
+      <c r="J35" s="32" t="n"/>
+      <c r="K35" s="32" t="n"/>
+      <c r="L35" s="32" t="n"/>
+      <c r="M35" s="32" t="n"/>
+      <c r="N35" s="32" t="n"/>
+      <c r="O35" s="32" t="n"/>
+      <c r="P35" s="32" t="n"/>
+      <c r="Q35" s="32" t="n"/>
+      <c r="R35" s="32" t="n"/>
+      <c r="S35" s="32" t="n"/>
+      <c r="T35" s="32" t="n"/>
+      <c r="U35" s="32" t="n"/>
+      <c r="V35" s="32" t="n"/>
+      <c r="W35" s="32" t="n"/>
+      <c r="X35" s="32" t="n"/>
+      <c r="Y35" s="32" t="n"/>
+      <c r="Z35" s="32" t="n"/>
+      <c r="AA35" s="32" t="n"/>
+      <c r="AB35" s="32" t="n"/>
+      <c r="AC35" s="39" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="31" t="inlineStr">
         <is>
           <t>■ 業務への示唆</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="B34" s="32" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="32" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="32" t="n"/>
-      <c r="H34" s="32" t="n"/>
-      <c r="I34" s="32" t="n"/>
-      <c r="J34" s="32" t="n"/>
-      <c r="K34" s="32" t="n"/>
-      <c r="L34" s="32" t="n"/>
-      <c r="M34" s="32" t="n"/>
-      <c r="N34" s="32" t="n"/>
-      <c r="O34" s="32" t="n"/>
-      <c r="P34" s="32" t="n"/>
-      <c r="Q34" s="32" t="n"/>
-      <c r="R34" s="32" t="n"/>
-      <c r="S34" s="32" t="n"/>
-      <c r="T34" s="32" t="n"/>
-      <c r="U34" s="32" t="n"/>
-      <c r="V34" s="32" t="n"/>
-      <c r="W34" s="32" t="n"/>
-      <c r="X34" s="32" t="n"/>
-      <c r="Y34" s="32" t="n"/>
-      <c r="Z34" s="32" t="n"/>
-      <c r="AA34" s="32" t="n"/>
-      <c r="AB34" s="32" t="n"/>
-      <c r="AC34" s="32" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="33" t="inlineStr">
-        <is>
-          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
-これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
-・子供001：平均欠席日数は約1.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
-・子供002：平均欠席日数は約1.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
-        </is>
-      </c>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
-      <c r="J35" s="34" t="n"/>
-      <c r="K35" s="34" t="n"/>
-      <c r="L35" s="34" t="n"/>
-      <c r="M35" s="34" t="n"/>
-      <c r="N35" s="34" t="n"/>
-      <c r="O35" s="34" t="n"/>
-      <c r="P35" s="34" t="n"/>
-      <c r="Q35" s="34" t="n"/>
-      <c r="R35" s="34" t="n"/>
-      <c r="S35" s="34" t="n"/>
-      <c r="T35" s="34" t="n"/>
-      <c r="U35" s="34" t="n"/>
-      <c r="V35" s="34" t="n"/>
-      <c r="W35" s="34" t="n"/>
-      <c r="X35" s="34" t="n"/>
-      <c r="Y35" s="34" t="n"/>
-      <c r="Z35" s="34" t="n"/>
-      <c r="AA35" s="34" t="n"/>
-      <c r="AB35" s="34" t="n"/>
-      <c r="AC35" s="35" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="36" t="n"/>
-      <c r="AC36" s="37" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="36" t="n"/>
-      <c r="AC37" s="37" t="n"/>
-    </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="B38" s="36" t="n"/>
-      <c r="AC38" s="37" t="n"/>
+      <c r="B38" s="32" t="n"/>
+      <c r="C38" s="32" t="n"/>
+      <c r="D38" s="32" t="n"/>
+      <c r="E38" s="32" t="n"/>
+      <c r="F38" s="32" t="n"/>
+      <c r="G38" s="32" t="n"/>
+      <c r="H38" s="32" t="n"/>
+      <c r="I38" s="32" t="n"/>
+      <c r="J38" s="32" t="n"/>
+      <c r="K38" s="32" t="n"/>
+      <c r="L38" s="32" t="n"/>
+      <c r="M38" s="32" t="n"/>
+      <c r="N38" s="32" t="n"/>
+      <c r="O38" s="32" t="n"/>
+      <c r="P38" s="32" t="n"/>
+      <c r="Q38" s="32" t="n"/>
+      <c r="R38" s="32" t="n"/>
+      <c r="S38" s="32" t="n"/>
+      <c r="T38" s="32" t="n"/>
+      <c r="U38" s="32" t="n"/>
+      <c r="V38" s="32" t="n"/>
+      <c r="W38" s="32" t="n"/>
+      <c r="X38" s="32" t="n"/>
+      <c r="Y38" s="32" t="n"/>
+      <c r="Z38" s="32" t="n"/>
+      <c r="AA38" s="32" t="n"/>
+      <c r="AB38" s="32" t="n"/>
+      <c r="AC38" s="32" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="36" t="n"/>
-      <c r="AC39" s="37" t="n"/>
+      <c r="B39" s="33" t="inlineStr">
+        <is>
+          <t>【子供001】
+データが不足しているため、判定できませんでした。
+【子供002】
+データが不足しているため、判定できませんでした。</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="34" t="n"/>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="34" t="n"/>
+      <c r="G39" s="34" t="n"/>
+      <c r="H39" s="34" t="n"/>
+      <c r="I39" s="34" t="n"/>
+      <c r="J39" s="34" t="n"/>
+      <c r="K39" s="34" t="n"/>
+      <c r="L39" s="34" t="n"/>
+      <c r="M39" s="34" t="n"/>
+      <c r="N39" s="34" t="n"/>
+      <c r="O39" s="34" t="n"/>
+      <c r="P39" s="34" t="n"/>
+      <c r="Q39" s="34" t="n"/>
+      <c r="R39" s="34" t="n"/>
+      <c r="S39" s="34" t="n"/>
+      <c r="T39" s="34" t="n"/>
+      <c r="U39" s="34" t="n"/>
+      <c r="V39" s="34" t="n"/>
+      <c r="W39" s="34" t="n"/>
+      <c r="X39" s="34" t="n"/>
+      <c r="Y39" s="34" t="n"/>
+      <c r="Z39" s="34" t="n"/>
+      <c r="AA39" s="34" t="n"/>
+      <c r="AB39" s="34" t="n"/>
+      <c r="AC39" s="35" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="B40" s="36" t="n"/>
@@ -2036,13 +2035,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B22:AC23"/>
     <mergeCell ref="B2:AC3"/>
-    <mergeCell ref="B24:AC31"/>
-    <mergeCell ref="B33:AC34"/>
-    <mergeCell ref="B6:AC21"/>
-    <mergeCell ref="B35:AC47"/>
+    <mergeCell ref="B25:AC26"/>
+    <mergeCell ref="B37:AC38"/>
+    <mergeCell ref="B27:AC35"/>
+    <mergeCell ref="B6:AC24"/>
     <mergeCell ref="B4:AC5"/>
+    <mergeCell ref="B39:AC47"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" scale="99"/>
@@ -2058,7 +2057,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -2097,7 +2096,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -2136,7 +2135,7 @@
   <dimension ref="B2:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -2175,7 +2174,7 @@
   <dimension ref="B2:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
@@ -2187,7 +2186,7 @@
     </row>
     <row r="3" ht="15" customHeight="1"/>
     <row r="4" ht="15" customHeight="1">
-      <c r="B4" s="30" t="inlineStr">
+      <c r="B4" s="31" t="inlineStr">
         <is>
           <t>■ 考察</t>
         </is>
@@ -2226,12 +2225,10 @@
     <row r="6" ht="15" customHeight="1">
       <c r="B6" s="33" t="inlineStr">
         <is>
-          <t>月齢別のデータが不足しているため、傾向は判定できませんでした。
-学年別のデータが不足しているため、傾向は判定できませんでした。
-登園月数別のデータが不足しているため、傾向は判定できませんでした。
-登園年数別のデータが不足しているため、傾向は判定できませんでした。
-月別の季節性のデータが不足しているため、傾向は判定できませんでした。
-月間推移のデータが不足しているため、傾向は判定できませんでした。</t>
+          <t>【子供001】
+データが不足しているため、判定できませんでした。
+【子供002】
+データが不足しているため、判定できませんでした。</t>
         </is>
       </c>
       <c r="C6" s="34" t="n"/>
@@ -2361,7 +2358,7 @@
       <c r="AC24" s="39" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="30" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
         <is>
           <t>■ 業務改善提案</t>
         </is>
@@ -2400,10 +2397,10 @@
     <row r="28" ht="15" customHeight="1">
       <c r="B28" s="33" t="inlineStr">
         <is>
-          <t>過去データおよびAI予測結果を踏まえると、年齢や登園初期、季節要因によって欠席日数が増加する傾向が確認された。
-これらの時期には感染症対策や健康観察を強化するとともに、家庭との情報共有を継続することが重要である。
-・子供001：平均欠席日数は約1.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。
-・子供002：平均欠席日数は約1.0日と予測され、予測期間内では安定基準への到達が見込まれなかった。健康観察を継続するとともに、家庭との情報共有や個別支援を強化することが望ましい。</t>
+          <t>【子供001】
+データが不足しているため、判定できませんでした。
+【子供002】
+データが不足しているため、判定できませんでした。</t>
         </is>
       </c>
       <c r="C28" s="34" t="n"/>
@@ -2550,7 +2547,7 @@
   <dimension ref="B2:AC3"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="2.59765625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col width="2.59765625" customWidth="1" style="31" min="1" max="16384"/>
+    <col width="2.59765625" customWidth="1" style="30" min="1" max="16384"/>
   </cols>
   <sheetData>
     <row r="2" ht="15" customHeight="1">
